--- a/multi seed generators/merged 10 seeds/classification/results/aggregated/fidelity_mean_sd.xlsx
+++ b/multi seed generators/merged 10 seeds/classification/results/aggregated/fidelity_mean_sd.xlsx
@@ -1398,12 +1398,10 @@
       <c r="O18" s="2" t="n">
         <v>0.7079166666666666</v>
       </c>
-      <c r="P18" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P18" s="2"/>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.707917 ± 0</t>
+          <t xml:space="preserve">0.707917</t>
         </is>
       </c>
       <c r="R18" s="2" t="n">
@@ -1469,12 +1467,10 @@
       <c r="O19" t="n">
         <v>0.3760959102831625</v>
       </c>
-      <c r="P19" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P19"/>
       <c r="Q19" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.376096 ± 0</t>
+          <t xml:space="preserve">0.376096</t>
         </is>
       </c>
       <c r="R19" t="n">
@@ -1540,12 +1536,10 @@
       <c r="O20" s="2" t="n">
         <v>0.7883588541666666</v>
       </c>
-      <c r="P20" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P20" s="2"/>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.788359 ± 0</t>
+          <t xml:space="preserve">0.788359</t>
         </is>
       </c>
       <c r="R20" s="2" t="n">
@@ -1611,12 +1605,10 @@
       <c r="O21" t="n">
         <v>2115.559874999999</v>
       </c>
-      <c r="P21" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P21"/>
       <c r="Q21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115.56 ± 0</t>
+          <t xml:space="preserve">2115.56</t>
         </is>
       </c>
       <c r="R21" t="n">
@@ -3670,12 +3662,10 @@
       <c r="O50" s="2" t="n">
         <v>0.870238445056627</v>
       </c>
-      <c r="P50" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P50" s="2"/>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.870238 ± 0</t>
+          <t xml:space="preserve">0.870238</t>
         </is>
       </c>
       <c r="R50" s="2" t="n">
@@ -5942,12 +5932,10 @@
       <c r="O82" s="2" t="n">
         <v>0.872857142857143</v>
       </c>
-      <c r="P82" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P82" s="2"/>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.872857 ± 0</t>
+          <t xml:space="preserve">0.872857</t>
         </is>
       </c>
       <c r="R82" s="2" t="n">
@@ -6013,12 +6001,10 @@
       <c r="O83" t="n">
         <v>0.009848353633469697</v>
       </c>
-      <c r="P83" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P83"/>
       <c r="Q83" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.00984835 ± 0</t>
+          <t xml:space="preserve">0.00984835</t>
         </is>
       </c>
       <c r="R83" t="n">
@@ -6084,12 +6070,10 @@
       <c r="O84" s="2" t="n">
         <v>0.8551804329462944</v>
       </c>
-      <c r="P84" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P84" s="2"/>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.85518 ± 0</t>
+          <t xml:space="preserve">0.85518</t>
         </is>
       </c>
       <c r="R84" s="2" t="n">
@@ -6155,12 +6139,10 @@
       <c r="O85" t="n">
         <v>90.60117857142856</v>
       </c>
-      <c r="P85" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P85"/>
       <c r="Q85" t="inlineStr">
         <is>
-          <t xml:space="preserve">90.6012 ± 0</t>
+          <t xml:space="preserve">90.6012</t>
         </is>
       </c>
       <c r="R85" t="n">
@@ -8214,12 +8196,10 @@
       <c r="O114" s="2" t="n">
         <v>0.9530795454545457</v>
       </c>
-      <c r="P114" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P114" s="2"/>
       <c r="Q114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.95308 ± 0</t>
+          <t xml:space="preserve">0.95308</t>
         </is>
       </c>
       <c r="R114" s="2" t="n">
@@ -8285,12 +8265,10 @@
       <c r="O115" t="n">
         <v>0.06812873655465546</v>
       </c>
-      <c r="P115" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P115"/>
       <c r="Q115" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0681287 ± 0</t>
+          <t xml:space="preserve">0.0681287</t>
         </is>
       </c>
       <c r="R115" t="n">
@@ -8356,12 +8334,10 @@
       <c r="O116" s="2" t="n">
         <v>0.9111395202020203</v>
       </c>
-      <c r="P116" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P116" s="2"/>
       <c r="Q116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.91114 ± 0</t>
+          <t xml:space="preserve">0.91114</t>
         </is>
       </c>
       <c r="R116" s="2" t="n">
@@ -8427,12 +8403,10 @@
       <c r="O117" t="n">
         <v>0.7336818181818183</v>
       </c>
-      <c r="P117" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P117"/>
       <c r="Q117" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.733682 ± 0</t>
+          <t xml:space="preserve">0.733682</t>
         </is>
       </c>
       <c r="R117" t="n">
@@ -10482,12 +10456,10 @@
       <c r="O146" s="2" t="n">
         <v>0.9201659340659342</v>
       </c>
-      <c r="P146" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P146" s="2"/>
       <c r="Q146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.920166 ± 0</t>
+          <t xml:space="preserve">0.920166</t>
         </is>
       </c>
       <c r="R146" s="2" t="n">
@@ -12754,12 +12726,10 @@
       <c r="O178" s="2" t="n">
         <v>0.976595454545454</v>
       </c>
-      <c r="P178" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P178" s="2"/>
       <c r="Q178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.976595 ± 0</t>
+          <t xml:space="preserve">0.976595</t>
         </is>
       </c>
       <c r="R178" s="2" t="n">
@@ -12825,12 +12795,10 @@
       <c r="O179" t="n">
         <v>0.02178163914459408</v>
       </c>
-      <c r="P179" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P179"/>
       <c r="Q179" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0217816 ± 0</t>
+          <t xml:space="preserve">0.0217816</t>
         </is>
       </c>
       <c r="R179" t="n">
@@ -12896,12 +12864,10 @@
       <c r="O180" s="2" t="n">
         <v>0.922098933618383</v>
       </c>
-      <c r="P180" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P180" s="2"/>
       <c r="Q180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.922099 ± 0</t>
+          <t xml:space="preserve">0.922099</t>
         </is>
       </c>
       <c r="R180" s="2" t="n">
@@ -12967,12 +12933,10 @@
       <c r="O181" t="n">
         <v>6.416240909090908</v>
       </c>
-      <c r="P181" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P181"/>
       <c r="Q181" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.41624 ± 0</t>
+          <t xml:space="preserve">6.41624</t>
         </is>
       </c>
       <c r="R181" t="n">
@@ -13677,12 +13641,10 @@
       <c r="O191" t="n">
         <v>0.334484855433916</v>
       </c>
-      <c r="P191" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P191"/>
       <c r="Q191" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.334485 ± 0</t>
+          <t xml:space="preserve">0.334485</t>
         </is>
       </c>
       <c r="R191" t="n">
@@ -15026,12 +14988,10 @@
       <c r="O210" s="2" t="n">
         <v>0.9134500000000003</v>
       </c>
-      <c r="P210" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P210" s="2"/>
       <c r="Q210" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.91345 ± 0</t>
+          <t xml:space="preserve">0.91345</t>
         </is>
       </c>
       <c r="R210" s="2" t="n">
@@ -15097,12 +15057,10 @@
       <c r="O211" t="n">
         <v>0.027986716920793457</v>
       </c>
-      <c r="P211" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P211"/>
       <c r="Q211" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0279867 ± 0</t>
+          <t xml:space="preserve">0.0279867</t>
         </is>
       </c>
       <c r="R211" t="n">
@@ -15168,12 +15126,10 @@
       <c r="O212" s="2" t="n">
         <v>0.8893182921814837</v>
       </c>
-      <c r="P212" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P212" s="2"/>
       <c r="Q212" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.889318 ± 0</t>
+          <t xml:space="preserve">0.889318</t>
         </is>
       </c>
       <c r="R212" s="2" t="n">
@@ -15239,12 +15195,10 @@
       <c r="O213" t="n">
         <v>5.20352194</v>
       </c>
-      <c r="P213" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P213"/>
       <c r="Q213" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.20352 ± 0</t>
+          <t xml:space="preserve">5.20352</t>
         </is>
       </c>
       <c r="R213" t="n">
@@ -17298,12 +17252,10 @@
       <c r="O242" s="2" t="n">
         <v>0.9239166666666666</v>
       </c>
-      <c r="P242" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P242" s="2"/>
       <c r="Q242" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.923917 ± 0</t>
+          <t xml:space="preserve">0.923917</t>
         </is>
       </c>
       <c r="R242" s="2" t="n">
@@ -17369,12 +17321,10 @@
       <c r="O243" t="n">
         <v>0.009532587279207694</v>
       </c>
-      <c r="P243" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P243"/>
       <c r="Q243" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.00953259 ± 0</t>
+          <t xml:space="preserve">0.00953259</t>
         </is>
       </c>
       <c r="R243" t="n">
@@ -17440,12 +17390,10 @@
       <c r="O244" s="2" t="n">
         <v>0.8985806959757218</v>
       </c>
-      <c r="P244" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P244" s="2"/>
       <c r="Q244" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.898581 ± 0</t>
+          <t xml:space="preserve">0.898581</t>
         </is>
       </c>
       <c r="R244" s="2" t="n">
@@ -17511,12 +17459,10 @@
       <c r="O245" t="n">
         <v>0.703003333333333</v>
       </c>
-      <c r="P245" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P245"/>
       <c r="Q245" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.703003 ± 0</t>
+          <t xml:space="preserve">0.703003</t>
         </is>
       </c>
       <c r="R245" t="n">
@@ -19570,12 +19516,10 @@
       <c r="O274" s="2" t="n">
         <v>0.893395695082525</v>
       </c>
-      <c r="P274" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P274" s="2"/>
       <c r="Q274" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.893396 ± 0</t>
+          <t xml:space="preserve">0.893396</t>
         </is>
       </c>
       <c r="R274" s="2" t="n">
@@ -19641,12 +19585,10 @@
       <c r="O275" t="n">
         <v>0.0742191093104625</v>
       </c>
-      <c r="P275" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P275"/>
       <c r="Q275" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0742191 ± 0</t>
+          <t xml:space="preserve">0.0742191</t>
         </is>
       </c>
       <c r="R275" t="n">
@@ -19712,12 +19654,10 @@
       <c r="O276" s="2" t="n">
         <v>0.9382852305742174</v>
       </c>
-      <c r="P276" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P276" s="2"/>
       <c r="Q276" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.938285 ± 0</t>
+          <t xml:space="preserve">0.938285</t>
         </is>
       </c>
       <c r="R276" s="2" t="n">
@@ -19783,12 +19723,10 @@
       <c r="O277" t="n">
         <v>0.33973922097399606</v>
       </c>
-      <c r="P277" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P277"/>
       <c r="Q277" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.339739 ± 0</t>
+          <t xml:space="preserve">0.339739</t>
         </is>
       </c>
       <c r="R277" t="n">
